--- a/data/trans_bre/IP07_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP07_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-5,86</t>
+          <t>-2,65</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-7,64%</t>
+          <t>-3,51%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 15,71</t>
+          <t>-9,79; 15,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 21,35</t>
+          <t>-6,67; 21,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,43; 12,01</t>
+          <t>-15,24; 12,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,63; 7,1</t>
+          <t>-16,96; 10,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,98; 23,18</t>
+          <t>-12,02; 22,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 39,31</t>
+          <t>-9,38; 39,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-20,27; 19,41</t>
+          <t>-20,34; 19,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-29,68; 9,78</t>
+          <t>-20,93; 15,15</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,08</t>
+          <t>-2,36</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>-2,94%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 9,64</t>
+          <t>-9,01; 10,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 5,29</t>
+          <t>-13,01; 5,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 12,5</t>
+          <t>-2,38; 13,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 15,61</t>
+          <t>-13,09; 7,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 13,56</t>
+          <t>-11,39; 14,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,6; 7,2</t>
+          <t>-16,13; 7,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 15,48</t>
+          <t>-2,44; 16,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 21,68</t>
+          <t>-15,47; 10,07</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,3</t>
+          <t>-3,17</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-3,75%</t>
+          <t>-3,61%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,43; 10,52</t>
+          <t>-13,93; 10,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,31; 5,28</t>
+          <t>-20,51; 6,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,3; 2,59</t>
+          <t>-11,37; 1,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 7,04</t>
+          <t>-13,95; 6,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,35; 15,04</t>
+          <t>-17,41; 14,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-25,74; 8,01</t>
+          <t>-27,53; 10,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 2,71</t>
+          <t>-11,53; 1,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-14,03; 8,24</t>
+          <t>-15,47; 7,51</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14,96</t>
+          <t>13,28</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>18,11%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 15,74</t>
+          <t>-6,97; 16,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 10,08</t>
+          <t>-10,81; 9,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 22,07</t>
+          <t>-4,31; 22,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 43,48</t>
+          <t>-1,69; 38,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 25,96</t>
+          <t>-9,22; 26,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 13,24</t>
+          <t>-12,98; 12,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 57,05</t>
+          <t>-9,07; 54,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 105,17</t>
+          <t>-2,2; 72,95</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-3,66</t>
+          <t>-1,22</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-12,79%</t>
+          <t>-4,51%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 20,14</t>
+          <t>-6,35; 20,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 27,01</t>
+          <t>-3,22; 27,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 7,06</t>
+          <t>-4,91; 7,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,72; 11,84</t>
+          <t>-15,33; 14,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 30,38</t>
+          <t>-6,95; 29,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 46,78</t>
+          <t>-3,91; 49,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 7,74</t>
+          <t>-5,13; 7,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-53,75; 58,73</t>
+          <t>-46,62; 75,19</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,39</t>
+          <t>1,44</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 10,5</t>
+          <t>-13,69; 10,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 17,48</t>
+          <t>-13,86; 16,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 4,31</t>
+          <t>-7,87; 4,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 8,78</t>
+          <t>-6,86; 10,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 14,25</t>
+          <t>-15,94; 14,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-18,91; 32,5</t>
+          <t>-19,44; 31,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 4,53</t>
+          <t>-7,87; 4,71</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 10,13</t>
+          <t>-7,29; 11,68</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-4,84</t>
+          <t>-7,23</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-5,74%</t>
+          <t>-8,43%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 3,39</t>
+          <t>-11,5; 3,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 6,47</t>
+          <t>-12,45; 5,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 3,85</t>
+          <t>-6,72; 3,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 5,26</t>
+          <t>-15,68; 0,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 4,1</t>
+          <t>-13,07; 4,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,1; 9,23</t>
+          <t>-15,85; 7,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 4,21</t>
+          <t>-7,03; 3,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-14,86; 6,56</t>
+          <t>-17,57; 0,91</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5,77</t>
+          <t>6,5</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 10,83</t>
+          <t>-4,61; 10,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 9,74</t>
+          <t>-3,14; 9,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 4,79</t>
+          <t>-2,7; 4,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 14,66</t>
+          <t>-3,13; 16,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 15,59</t>
+          <t>-6,02; 14,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 12,2</t>
+          <t>-3,72; 11,99</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 5,18</t>
+          <t>-2,85; 5,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 23,59</t>
+          <t>-4,22; 27,15</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1,21</t>
+          <t>0,7</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 4,74</t>
+          <t>-2,71; 4,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 4,26</t>
+          <t>-3,11; 4,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 3,89</t>
+          <t>-1,7; 4,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 6,54</t>
+          <t>-3,72; 5,41</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 6,4</t>
+          <t>-3,43; 5,86</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 5,83</t>
+          <t>-4,09; 6,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 4,62</t>
+          <t>-1,92; 4,96</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 8,92</t>
+          <t>-4,79; 7,4</t>
         </is>
       </c>
     </row>
